--- a/outputs/evaluation/decision/v2/CF_M05/run_3/CF_M05_decision_eval_llm_report.xlsx
+++ b/outputs/evaluation/decision/v2/CF_M05/run_3/CF_M05_decision_eval_llm_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,51 +471,151 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>AD_04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Angular applies the MVVM pattern, as its architecture is based on components and services.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>C_02</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>AU_13, P_03</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>11a. Usability</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Angular; MVVM</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>CF_M05_AD10</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>When making the decision to use Angular for frontEnd development and Spring for the backEnd, several technological criteria were considered, the work methodology that would be implemented throughout the development of the application was thought about and the long-term maintainability of the project was taken into consideration.</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.6804</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>AD_05</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Angular applies the MVVM (Model-View-ViewModel) pattern, as its architecture is based on components and services.</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>C_02</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>P_03</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>11a. Usability</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>MVVM</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>CF_M05_AD10</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>When making the decision to use Angular for frontEnd development and Spring for the backEnd, several technological criteria were considered, the work methodology that would be implemented throughout the development of the application was thought about and the long-term maintainability of the project was taken into consideration.</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>0.6768999999999999</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Spring Boot organizes the code following the layered pattern with which responsibilities are separated.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Maintainability</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>AU_14, P_04</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Maintainability</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Spring Boot; Layered Architecture</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>CF_M05_AD12</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>This structure clarifies roles, avoids unnecessary coupling, and makes it easier to test, reuse, and maintain the code over time.</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.7287</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AD_06</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>AWS invests heavily in security and certifications, manages multiple levels of security and offers tools to protect data and infrastructures facilitating compliance with legal regulations and international standards.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AU_17</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Amazon Web Services (AWS)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>CF_M05_AD02</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>In addition to its routing task, this component incorporates protection mechanisms to ensure the integrity and confidentiality of communications.</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.7018</v>
       </c>
     </row>
   </sheetData>
